--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.02028658750097</v>
+        <v>8.290796570468908</v>
       </c>
       <c r="D2" t="n">
-        <v>50.12488875189364</v>
+        <v>8.145294422182717</v>
       </c>
       <c r="E2" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F2" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.24415257034869</v>
+        <v>5.564674792681662</v>
       </c>
       <c r="D3" t="n">
-        <v>33.40855134982377</v>
+        <v>5.428889594346364</v>
       </c>
       <c r="E3" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F3" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.12437569983809</v>
+        <v>7.49521105122369</v>
       </c>
       <c r="D4" t="n">
-        <v>45.40216318389714</v>
+        <v>7.377851517383285</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F4" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.1800868337067</v>
+        <v>6.366764110477339</v>
       </c>
       <c r="D5" t="n">
-        <v>38.45628115041945</v>
+        <v>6.249145686943161</v>
       </c>
       <c r="E5" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F5" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.26075055745524</v>
+        <v>4.104871965586477</v>
       </c>
       <c r="D6" t="n">
-        <v>24.59439493350326</v>
+        <v>3.996589176694279</v>
       </c>
       <c r="E6" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F6" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.224321052136001</v>
+        <v>1.1739521709721</v>
       </c>
       <c r="D7" t="n">
-        <v>6.313875418101245</v>
+        <v>1.026004755441452</v>
       </c>
       <c r="E7" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F7" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.06914368545072</v>
+        <v>2.286235848885743</v>
       </c>
       <c r="D8" t="n">
-        <v>13.61821794795794</v>
+        <v>2.212960416543165</v>
       </c>
       <c r="E8" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F8" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.70250471467072</v>
+        <v>2.876657016133993</v>
       </c>
       <c r="D9" t="n">
-        <v>17.97654174645843</v>
+        <v>2.921188033799495</v>
       </c>
       <c r="E9" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F9" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.19916595856477</v>
+        <v>4.744864468266776</v>
       </c>
       <c r="D10" t="n">
-        <v>29.99788634197298</v>
+        <v>4.874656530570609</v>
       </c>
       <c r="E10" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F10" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.90576796250313</v>
+        <v>5.509687293906758</v>
       </c>
       <c r="D11" t="n">
-        <v>34.17475877626462</v>
+        <v>5.553398301143001</v>
       </c>
       <c r="E11" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F11" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.44059270438089</v>
+        <v>4.296596314461895</v>
       </c>
       <c r="D12" t="n">
-        <v>27.23139371630908</v>
+        <v>4.425101478900226</v>
       </c>
       <c r="E12" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F12" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.70354967881069</v>
+        <v>5.314326822806737</v>
       </c>
       <c r="D13" t="n">
-        <v>33.3512077796132</v>
+        <v>5.419571264187146</v>
       </c>
       <c r="E13" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F13" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.9036712081997</v>
+        <v>2.421846571332452</v>
       </c>
       <c r="D14" t="n">
-        <v>15.78432236174439</v>
+        <v>2.564952383783464</v>
       </c>
       <c r="E14" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F14" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.38857433838811</v>
+        <v>2.175643329988068</v>
       </c>
       <c r="D15" t="n">
-        <v>13.46022297491781</v>
+        <v>2.187286233424144</v>
       </c>
       <c r="E15" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F15" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.43152574964957</v>
+        <v>6.895122934318056</v>
       </c>
       <c r="D16" t="n">
-        <v>43.31288056815499</v>
+        <v>7.038343092325186</v>
       </c>
       <c r="E16" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F16" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>4.786878659358474</v>
+        <v>0.7778677821457521</v>
       </c>
       <c r="D17" t="n">
-        <v>4.982226844328988</v>
+        <v>0.8096118622034606</v>
       </c>
       <c r="E17" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F17" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.68881620375005</v>
+        <v>3.361932633109383</v>
       </c>
       <c r="D18" t="n">
-        <v>20.57662101557482</v>
+        <v>3.343700915030908</v>
       </c>
       <c r="E18" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F18" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>26.60829184835975</v>
+        <v>4.323847425358459</v>
       </c>
       <c r="D19" t="n">
-        <v>26.5154117459351</v>
+        <v>4.308754408714455</v>
       </c>
       <c r="E19" t="n">
-        <v>12.86192195413625</v>
+        <v>2.09006231754714</v>
       </c>
       <c r="F19" t="n">
-        <v>12.77968448307027</v>
+        <v>2.076698728498919</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
